--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-165</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 813.085,90</t>
-  </si>
-  <si>
-    <t>R$ 4.567,90
-R$ 4.680,18</t>
-  </si>
-  <si>
-    <t>0.6%
-3.1%</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>(1.9%)</t>
+166</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>R$ 815.959,44</t>
+  </si>
+  <si>
+    <t>R$ 4.558,43
+R$ 4.669,29</t>
+  </si>
+  <si>
+    <t>0.4%
+3.0%</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>(2.0%)</t>
   </si>
   <si>
     <t>12.5%</t>
   </si>
   <si>
-    <t>(37.7%)</t>
+    <t>(37.5%)</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -950,10 +950,10 @@
     <t>26.2</t>
   </si>
   <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
+    <t>71.5%</t>
+  </si>
+  <si>
+    <t>8.8%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -962,7 +962,7 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>11.6</t>
+    <t>11.7</t>
   </si>
   <si>
     <t>18.3</t>
@@ -971,7 +971,7 @@
     <t>75.2%</t>
   </si>
   <si>
-    <t>-R$ 18.494,12</t>
+    <t>-R$ 18.556,12</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>4.0307465517241381</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>8.8709760000000006</v>
+      </c>
       <c r="AD13" s="8">
         <v>15.830460344827586</v>
       </c>
@@ -4952,7 +4954,9 @@
       <c r="AB28" s="8">
         <v>4.38678275862069</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>5.9155160000000002</v>
+      </c>
       <c r="AD28" s="8">
         <v>12.865517241379312</v>
       </c>
@@ -5829,7 +5833,9 @@
       <c r="AB35" s="8">
         <v>2.5104187499999999</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>4.7300230000000001</v>
+      </c>
       <c r="AD35" s="8">
         <v>11.726043750000001</v>
       </c>
@@ -5960,7 +5966,9 @@
       <c r="AB36" s="8">
         <v>9.5818826086956523</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>14.326154000000001</v>
+      </c>
       <c r="AD36" s="8">
         <v>17.763021875</v>
       </c>
@@ -6351,7 +6359,9 @@
       <c r="AB39" s="8">
         <v>3.4904761904761905</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>5.2750909999999998</v>
+      </c>
       <c r="AD39" s="8">
         <v>11.997999999999999</v>
       </c>
@@ -7744,7 +7754,9 @@
       <c r="AB50" s="8">
         <v>3.7608350000000002</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>6.6203560000000001</v>
+      </c>
       <c r="AD50" s="8">
         <v>14.223809523809523</v>
       </c>
@@ -8359,7 +8371,9 @@
       <c r="AB55" s="8">
         <v>25.355555555555554</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>28.046030999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>33.477192105263157</v>
       </c>
@@ -10841,7 +10855,9 @@
       <c r="AB75" s="8">
         <v>7.7857142857142856</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>12.680952</v>
+      </c>
       <c r="AD75" s="8">
         <v>19.615871428571428</v>
       </c>
@@ -12170,10 +12186,10 @@
         <v>-0.2857142857142857</v>
       </c>
       <c r="T86" s="6">
-        <v>0.34422366524357018</v>
+        <v>0.30769613556890518</v>
       </c>
       <c r="U86" s="6">
-        <v>-0.0065270813647931901</v>
+        <v>-0.043054611039458165</v>
       </c>
       <c r="V86" s="6">
         <v>0.04460597010807716</v>
@@ -12680,7 +12696,9 @@
       <c r="AB90" s="8">
         <v>25.862036111111113</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>31.672557999999999</v>
+      </c>
       <c r="AD90" s="8">
         <v>39.683783783783781</v>
       </c>
@@ -18454,7 +18472,9 @@
       <c r="AB136" s="8">
         <v>9.2133349999999989</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="8">
+        <v>13.642499000000001</v>
+      </c>
       <c r="AD136" s="8">
         <v>20.560835000000001</v>
       </c>
@@ -19420,7 +19440,9 @@
       <c r="AB144" s="8">
         <v>2.6133338461538465</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>5.0901439999999996</v>
+      </c>
       <c r="AD144" s="8">
         <v>11.794117647058824</v>
       </c>
@@ -20956,7 +20978,9 @@
       <c r="AB156" s="8">
         <v>7.0970250000000004</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>12.299403</v>
+      </c>
       <c r="AD156" s="8">
         <v>19.238096428571428</v>
       </c>
@@ -23259,7 +23283,9 @@
       <c r="AB175" s="8">
         <v>4.2833352941176468</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>10.438888</v>
+      </c>
       <c r="AD175" s="8">
         <v>17.089816666666664</v>
       </c>
@@ -24033,7 +24059,9 @@
       <c r="AB181" s="8">
         <v>1.5071428571428573</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>4.312697</v>
+      </c>
       <c r="AD181" s="8">
         <v>10.26</v>
       </c>
@@ -24779,7 +24807,9 @@
       <c r="AB187" s="8">
         <v>14.727452941176471</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>25.814703999999999</v>
+      </c>
       <c r="AD187" s="8">
         <v>32.766664705882356</v>
       </c>
@@ -25172,7 +25202,9 @@
       <c r="AB190" s="8">
         <v>3.302775</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>7.4181609999999996</v>
+      </c>
       <c r="AD190" s="8">
         <v>13.979484615384617</v>
       </c>
@@ -25823,7 +25855,9 @@
       <c r="AB195" s="8">
         <v>4.3628205128205133</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>8.0773489999999999</v>
+      </c>
       <c r="AD195" s="8">
         <v>15.017094871794871</v>
       </c>
@@ -26267,7 +26301,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -26303,25 +26337,59 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
+      <c r="O199" s="5">
+        <v>2873.54</v>
+      </c>
+      <c r="P199" s="5">
+        <v>2873.54</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.28843006108991143</v>
+      </c>
+      <c r="R199" s="7">
+        <v>34</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.24444444444444446</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.36403157777514839</v>
+      </c>
+      <c r="U199" s="6">
+        <v>0.36403157777514839</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.015211202906519485</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-0.022206059424960154</v>
+      </c>
+      <c r="X199" s="8">
+        <v>24.418749999999999</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.4375</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>5.4600999999999997</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>4.8770812499999998</v>
+      </c>
       <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="AD199" s="8">
+        <v>17.853124999999999</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.8125</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-62</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -26440,7 +26508,9 @@
       <c r="AB200" s="8">
         <v>2.0708333333333333</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>10.555555</v>
+      </c>
       <c r="AD200" s="8">
         <v>17.515274999999999</v>
       </c>
@@ -27013,7 +27083,9 @@
       <c r="AB205" s="8">
         <v>1.6060636363636362</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>8.4602260000000005</v>
+      </c>
       <c r="AD205" s="8">
         <v>15.141666666666666</v>
       </c>
@@ -27138,7 +27210,9 @@
       <c r="AB206" s="8">
         <v>4.2772727272727273</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>13.097784000000001</v>
+      </c>
       <c r="AD206" s="8">
         <v>18.985900000000001</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-166</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 815.959,44</t>
-  </si>
-  <si>
-    <t>R$ 4.558,43
-R$ 4.669,29</t>
+167</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 821.061,47</t>
+  </si>
+  <si>
+    <t>R$ 4.561,45
+R$ 4.671,88</t>
   </si>
   <si>
     <t>0.4%
 3.0%</t>
   </si>
   <si>
-    <t>51.4</t>
+    <t>51.5</t>
   </si>
   <si>
     <t>(2.0%)</t>
   </si>
   <si>
-    <t>12.5%</t>
-  </si>
-  <si>
-    <t>(37.5%)</t>
+    <t>12.7%</t>
+  </si>
+  <si>
+    <t>(37.2%)</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -950,7 +950,7 @@
     <t>26.2</t>
   </si>
   <si>
-    <t>71.5%</t>
+    <t>71.6%</t>
   </si>
   <si>
     <t>8.8%</t>
@@ -6674,7 +6674,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6710,25 +6710,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>5102.0299999999997</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5102.0299999999997</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.044842783009014786</v>
+      </c>
+      <c r="R42" s="7">
+        <v>56</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.037037037037036979</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.33499522738988208</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.02768421589053769</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.044385274096781092</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.00056350119462253261</v>
+      </c>
+      <c r="X42" s="8">
+        <v>26.681667499999996</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.3173076923076925</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>6.0870825000000002</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>18.749582499999999</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.77500000000000002</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -17166,7 +17200,9 @@
       <c r="AB126" s="8">
         <v>14.118668</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>19.698793999999999</v>
+      </c>
       <c r="AD126" s="8">
         <v>26.695331999999997</v>
       </c>
@@ -20701,7 +20737,7 @@
         <v>0.014173938503526558</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.015855392836042516</v>
+        <v>-0.012415103809937102</v>
       </c>
       <c r="X154" s="8">
         <v>25.805558333333334</v>
@@ -26379,7 +26415,9 @@
       <c r="AB199" s="8">
         <v>4.8770812499999998</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>10.913541</v>
+      </c>
       <c r="AD199" s="8">
         <v>17.853124999999999</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -912,30 +912,30 @@
   </si>
   <si>
     <t>214
-167</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 821.061,47</t>
-  </si>
-  <si>
-    <t>R$ 4.561,45
-R$ 4.671,88</t>
+168</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 825.046,47</t>
+  </si>
+  <si>
+    <t>R$ 4.558,27
+R$ 4.667,80</t>
   </si>
   <si>
     <t>0.4%
-3.0%</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>(2.0%)</t>
-  </si>
-  <si>
-    <t>12.7%</t>
+2.9%</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>(2.1%)</t>
+  </si>
+  <si>
+    <t>12.6%</t>
   </si>
   <si>
     <t>(37.2%)</t>
@@ -950,10 +950,10 @@
     <t>26.2</t>
   </si>
   <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
+    <t>71.3%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -968,10 +968,10 @@
     <t>18.3</t>
   </si>
   <si>
-    <t>75.2%</t>
-  </si>
-  <si>
-    <t>-R$ 18.556,12</t>
+    <t>75.0%</t>
+  </si>
+  <si>
+    <t>-R$ 18.629,92</t>
   </si>
   <si>
     <t>2.94</t>
@@ -6752,7 +6752,9 @@
       <c r="AB42" s="8">
         <v>6.0870825000000002</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>11.854562</v>
+      </c>
       <c r="AD42" s="8">
         <v>18.749582499999999</v>
       </c>
@@ -14180,7 +14182,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14216,25 +14218,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>3985</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3985</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.033524688169226491</v>
+      </c>
+      <c r="R102" s="7">
+        <v>35</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.22222222222222221</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.00031656210790464241</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33629824341279801</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.015496110414052699</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0055302383939774156</v>
+      </c>
+      <c r="X102" s="8">
+        <v>35.909524999999995</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.39285714285714285</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>7.3761270270270272</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>13.843940909090911</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>21.443383000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>24.269046428571432</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.32142857142857145</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>-73.799999999999997</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -911,49 +911,52 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-168</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 825.046,47</t>
-  </si>
-  <si>
-    <t>R$ 4.558,27
-R$ 4.667,80</t>
-  </si>
-  <si>
-    <t>0.4%
-2.9%</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>(2.1%)</t>
-  </si>
-  <si>
-    <t>12.6%</t>
-  </si>
-  <si>
-    <t>(37.2%)</t>
-  </si>
-  <si>
-    <t>3.8%</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+171</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 842.624,77</t>
+  </si>
+  <si>
+    <t>R$ 4.579,48
+R$ 4.688,70</t>
+  </si>
+  <si>
+    <t>0.7%
+3.2%</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>(1.7%)</t>
+  </si>
+  <si>
+    <t>13.5%</t>
+  </si>
+  <si>
+    <t>(36.1%)</t>
+  </si>
+  <si>
+    <t>3.9%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.2</t>
-  </si>
-  <si>
-    <t>71.3%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>71.5%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -962,7 +965,7 @@
     <t>6.8</t>
   </si>
   <si>
-    <t>11.7</t>
+    <t>11.8</t>
   </si>
   <si>
     <t>18.3</t>
@@ -971,7 +974,7 @@
     <t>75.0%</t>
   </si>
   <si>
-    <t>-R$ 18.629,92</t>
+    <t>-R$ 18.766,52</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2213,10 +2216,10 @@
         <v>0.13636363636363646</v>
       </c>
       <c r="T7" s="6">
-        <v>0.53616996791956528</v>
+        <v>0.4840521829445168</v>
       </c>
       <c r="U7" s="6">
-        <v>0.034455324000098327</v>
+        <v>-0.017662460974950219</v>
       </c>
       <c r="V7" s="6">
         <v>0.046552736055458586</v>
@@ -5658,7 +5661,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5694,25 +5697,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>9011.8600000000006</v>
+      </c>
+      <c r="P34" s="5">
+        <v>9011.8600000000006</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.26918310208266427</v>
+      </c>
+      <c r="R34" s="7">
+        <v>111</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.47999999999999998</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.65737920917546422</v>
+      </c>
+      <c r="U34" s="6">
+        <v>0.29773092347195801</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.050678938643077008</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.021310972429664909</v>
+      </c>
+      <c r="X34" s="8">
+        <v>20.272463768115941</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.94202898550724634</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.028985507246376812</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>7.5350961538461538</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.7719811594202897</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>10.609902</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>16.569323188405797</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.91304347826086951</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>-59.899999999999999</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5807,10 +5846,10 @@
         <v>0.14285714285714279</v>
       </c>
       <c r="T35" s="6">
-        <v>0.79448764994028342</v>
+        <v>0.44528185022992284</v>
       </c>
       <c r="U35" s="6">
-        <v>0.47669213992695547</v>
+        <v>0.12748634021659483</v>
       </c>
       <c r="V35" s="6">
         <v>0.12903417974947928</v>
@@ -10944,7 +10983,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10978,25 +11017,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>6626.8299999999999</v>
+      </c>
+      <c r="P76" s="5">
+        <v>6626.8299999999999</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.16551554324407514</v>
+      </c>
+      <c r="R76" s="7">
+        <v>86</v>
+      </c>
+      <c r="S76" s="6">
+        <v>0.16216216216216206</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.6883635916418559</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0.27717151337819135</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.065418835250036597</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.0336042270587898</v>
+      </c>
+      <c r="X76" s="8">
+        <v>37.526810869565217</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.1384615384615389</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>13.313513513513515</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>16.380784999999999</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>22.07463695652174</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.45652173913043476</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-76.700000000000003</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -15944,7 +16019,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>19.809847000000001</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19081,7 +19158,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19117,25 +19194,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>1939.6099999999999</v>
+      </c>
+      <c r="P141" s="5">
+        <v>1939.6099999999999</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>-0.16563712542909503</v>
+      </c>
+      <c r="R141" s="7">
+        <v>21</v>
+      </c>
+      <c r="S141" s="6">
+        <v>-0.30000000000000004</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.39310531498600237</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.074778434839993607</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.1812872175334217</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.08478328117508159</v>
+      </c>
+      <c r="X141" s="8">
+        <v>23.033333333333331</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>3.6614052631578944</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>3.4291666666666667</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>6.9583320000000004</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>14.909725</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28265,112 +28378,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 842.624,77</t>
-  </si>
-  <si>
-    <t>R$ 4.579,48
-R$ 4.688,70</t>
-  </si>
-  <si>
-    <t>0.7%
-3.2%</t>
-  </si>
-  <si>
-    <t>51.7</t>
+172</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 847.848,21</t>
+  </si>
+  <si>
+    <t>R$ 4.582,96
+R$ 4.691,81</t>
+  </si>
+  <si>
+    <t>0.5%
+3.0%</t>
+  </si>
+  <si>
+    <t>51.8</t>
   </si>
   <si>
     <t>(1.7%)</t>
   </si>
   <si>
-    <t>13.5%</t>
-  </si>
-  <si>
-    <t>(36.1%)</t>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>(35.9%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -953,7 +953,7 @@
     <t>26.3</t>
   </si>
   <si>
-    <t>71.5%</t>
+    <t>71.3%</t>
   </si>
   <si>
     <t>9.1%</t>
@@ -971,7 +971,7 @@
     <t>18.3</t>
   </si>
   <si>
-    <t>75.0%</t>
+    <t>74.7%</t>
   </si>
   <si>
     <t>-R$ 18.766,52</t>
@@ -11073,7 +11073,7 @@
         <v>-76.700000000000003</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16549,7 +16549,7 @@
         <v>-136.69999999999999</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21408,7 +21408,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21444,27 +21444,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>5223.4399999999996</v>
+      </c>
+      <c r="P159" s="5">
+        <v>5223.4399999999996</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.19203706138485221</v>
+      </c>
+      <c r="R159" s="7">
+        <v>59</v>
+      </c>
+      <c r="S159" s="6">
+        <v>-0.13235294117647056</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.25429626835954855</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.016596093761965296</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.053638981207786443</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.013127364342272525</v>
+      </c>
+      <c r="X159" s="8">
+        <v>32.818841304347828</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.17391304347826086</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>4.5320981481481484</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>5.4670282608695659</v>
+      </c>
       <c r="AC159" s="8">
         <v>10.147462000000001</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>17.075723913043479</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.36956521739130432</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>0</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-172</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 847.848,21</t>
-  </si>
-  <si>
-    <t>R$ 4.582,96
-R$ 4.691,81</t>
+173</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 852.412,72</t>
+  </si>
+  <si>
+    <t>R$ 4.582,86
+R$ 4.691,07</t>
   </si>
   <si>
     <t>0.5%
-3.0%</t>
-  </si>
-  <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>(1.7%)</t>
-  </si>
-  <si>
-    <t>13.6%</t>
-  </si>
-  <si>
-    <t>(35.9%)</t>
+2.9%</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>(1.8%)</t>
+  </si>
+  <si>
+    <t>13.5%</t>
+  </si>
+  <si>
+    <t>(35.8%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -950,13 +950,13 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>71.3%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
+    <t>26.4</t>
+  </si>
+  <si>
+    <t>71.4%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -971,7 +971,7 @@
     <t>18.3</t>
   </si>
   <si>
-    <t>74.7%</t>
+    <t>74.6%</t>
   </si>
   <si>
     <t>-R$ 18.766,52</t>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12636,7 +12636,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12670,25 +12670,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>4564.5100000000002</v>
+      </c>
+      <c r="P89" s="5">
+        <v>4564.5100000000002</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.092989937366864672</v>
+      </c>
+      <c r="R89" s="7">
+        <v>47</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.1132075471698113</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.016825683370175551</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.33149034617078282</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.022605602791975477</v>
+      </c>
+      <c r="W89" s="6">
+        <v>-0.0010420614699058607</v>
+      </c>
+      <c r="X89" s="8">
+        <v>40.831411538461538</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>7.1185613636363634</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.2423624999999996</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>21.747332</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.42307692307692307</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14218,7 +14252,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -24726,7 +24760,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25697,7 +25731,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27008,7 +27042,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28417,7 +28451,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-08).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-173</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 852.412,72</t>
-  </si>
-  <si>
-    <t>R$ 4.582,86
-R$ 4.691,07</t>
-  </si>
-  <si>
-    <t>0.5%
-2.9%</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>(1.8%)</t>
-  </si>
-  <si>
-    <t>13.5%</t>
-  </si>
-  <si>
-    <t>(35.8%)</t>
+179</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 871.125,58</t>
+  </si>
+  <si>
+    <t>R$ 4.537,11
+R$ 4.638,37</t>
+  </si>
+  <si>
+    <t>0.2%
+2.6%</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>(2.0%)</t>
+  </si>
+  <si>
+    <t>13.8%</t>
+  </si>
+  <si>
+    <t>(35.1%)</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -950,31 +950,31 @@
     <t>0.4%</t>
   </si>
   <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>71.4%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>6.8</t>
-  </si>
-  <si>
-    <t>11.8</t>
-  </si>
-  <si>
-    <t>18.3</t>
-  </si>
-  <si>
-    <t>74.6%</t>
-  </si>
-  <si>
-    <t>-R$ 18.766,52</t>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>71.8%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>-R$ 18.730,52</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>6172.8400000000001</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6172.8400000000001</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.023759028446624697</v>
+      </c>
+      <c r="R6" s="7">
+        <v>66</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.029411764705882359</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.2645240440380765</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.01010805399135568</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.046902803247775744</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0080049863596010906</v>
+      </c>
+      <c r="X6" s="8">
+        <v>19.209524489795918</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>4.5819887096774199</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.1364583333333331</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>6.7309020000000004</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>13.454761224489797</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>1</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7882,7 +7918,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7918,25 +7954,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>560.60000000000002</v>
+      </c>
+      <c r="P51" s="5">
+        <v>560.60000000000002</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.20150885164387677</v>
+      </c>
+      <c r="R51" s="7">
+        <v>5</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.16666666666666663</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.35602925437031752</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.073490902604352468</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.15485372814841242</v>
+      </c>
+      <c r="X51" s="8">
+        <v>20.866700000000002</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>7.306659999999999</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>4.7000000000000002</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>18.2667</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8809,7 +8879,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>15.232113</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20502,7 +20574,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20538,25 +20610,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2411.0300000000002</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2411.0300000000002</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.3940887318492754</v>
+      </c>
+      <c r="R151" s="7">
+        <v>30</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.34782608695652173</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.3828637968005375</v>
+      </c>
+      <c r="U151" s="6">
+        <v>0.067455029593161422</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.044185057838351235</v>
+      </c>
+      <c r="W151" s="6">
+        <v>-0.0097255115033823714</v>
+      </c>
+      <c r="X151" s="8">
+        <v>21.635714285714283</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>2.7548387096774194</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.0493814814814817</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>4.7220009999999997</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>11.567857142857141</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.9642857142857143</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21252,7 +21360,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21288,25 +21396,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>2315.3200000000002</v>
+      </c>
+      <c r="P157" s="5">
+        <v>2315.3200000000002</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.18183681402169682</v>
+      </c>
+      <c r="R157" s="7">
+        <v>29</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.064516129032258118</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.32925168011333206</v>
+      </c>
+      <c r="U157" s="6">
+        <v>1.2957172226733238E-06</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.062319463400307515</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.021214994039700775</v>
+      </c>
+      <c r="X157" s="8">
+        <v>26.060000000000002</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>6.8833346153846158</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>4.5973684210526313</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>11.613201</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>18.244999999999997</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21347,7 +21491,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21383,25 +21527,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>3665.52</v>
+      </c>
+      <c r="P158" s="5">
+        <v>3665.52</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>0.02127232758548625</v>
+      </c>
+      <c r="R158" s="7">
+        <v>32</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.2685986435758092</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0035912230733974992</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.037270564612933502</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0036600536895174491</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.656896551724138</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.86206896551724133</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>9.6295709677419357</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>4.1068965517241374</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>14.278734999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>21.214368965517238</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.41379310344827586</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22200,7 +22380,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22236,25 +22416,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>3587.5500000000002</v>
+      </c>
+      <c r="P165" s="5">
+        <v>3587.5500000000002</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.071511390164239907</v>
+      </c>
+      <c r="R165" s="7">
+        <v>44</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.13725490196078427</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.30675580828141769</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.012841131134060848</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.026869172555086338</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.011616702206241027</v>
+      </c>
+      <c r="X165" s="8">
+        <v>17.822465217391304</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>3.9821977272727271</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.1543478260869566</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>5.3007229999999996</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>12.250726086956522</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>36</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
